--- a/reports/pdf_change_20261019.xlsx
+++ b/reports/pdf_change_20261019.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억   ·   현금 199억(4.3%)      당일 2026-10-19  vs  전영업일 2026-10-16      매수 1종목  /  매도 0종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -691,7 +691,7 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억   ·   현금 59억(1.9%)      당일 2026-10-19  vs  전영업일 2026-10-16      매수 5종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 5종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B8" s="4" t="n"/>
@@ -952,7 +952,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억   ·   현금 40억(1.7%)      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -976,7 +976,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억   ·   현금 47억(2.4%)      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1000,7 +1000,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억   ·   현금 3억(1.3%)      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1065,7 +1065,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 766억   ·   현금 3억(0.4%)      당일 2026-10-19  vs  전영업일 2026-10-16      매수 8종목  /  매도 5종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 766억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 8종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1700,23 +1700,23 @@
       </c>
       <c r="G49" s="15" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>동국산업</t>
         </is>
       </c>
       <c r="H49" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I49" s="16" t="n">
-        <v>-213555452</v>
+        <v>-6919335</v>
       </c>
       <c r="J49" s="17" t="inlineStr">
         <is>
-          <t>2.91%→2.03%</t>
+          <t>1.83%→1.81%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>307→303</t>
         </is>
       </c>
     </row>
@@ -1728,23 +1728,23 @@
       <c r="E50" s="14" t="n"/>
       <c r="G50" s="15" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H50" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>-205241858</v>
+        <v>-213555452</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t>3.84%→3.01%</t>
+          <t>2.91%→2.03%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>21→17</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
@@ -1756,23 +1756,23 @@
       <c r="E51" s="14" t="n"/>
       <c r="G51" s="15" t="inlineStr">
         <is>
-          <t>동국산업</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H51" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I51" s="16" t="n">
-        <v>-6919335</v>
+        <v>-205241858</v>
       </c>
       <c r="J51" s="17" t="inlineStr">
         <is>
-          <t>1.83%→1.81%</t>
+          <t>3.84%→3.01%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>307→303</t>
+          <t>21→17</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261019.xlsx
+++ b/reports/pdf_change_20261019.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 1종목  /  매도 0종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,651억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>44</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>893882216</v>
+        <v>893881585</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 5종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,080억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 5종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B8" s="4" t="n"/>
@@ -787,7 +787,7 @@
         <v>39</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>871240862</v>
+        <v>874528430</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>-90</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>-612468254</v>
+        <v>-614779362</v>
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>597363248</v>
+        <v>599617358</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>-17</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>-1747940726</v>
+        <v>-1754536462</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>623280259</v>
+        <v>625632165</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>620100257</v>
+        <v>622440164</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>261184108</v>
+        <v>262169669</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,391억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -976,7 +976,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,004억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1000,7 +1000,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 276억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1065,7 +1065,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 766억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 8종목  /  매도 5종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 828억      당일 2026-10-19  vs  전영업일 2026-10-16      매수 8종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1161,7 +1161,7 @@
         <v>193</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>349978526</v>
+        <v>356885812</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>-72</v>
       </c>
       <c r="I34" s="16" t="n">
-        <v>-803289706</v>
+        <v>-819143683</v>
       </c>
       <c r="J34" s="17" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>96</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>245145632</v>
+        <v>249983903</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>-68</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>-310080041</v>
+        <v>-316199878</v>
       </c>
       <c r="J35" s="17" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>85</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>471580062</v>
+        <v>480887314</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>-39</v>
       </c>
       <c r="I36" s="16" t="n">
-        <v>-395397652</v>
+        <v>-403201344</v>
       </c>
       <c r="J36" s="17" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>76</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>355801647</v>
+        <v>362823860</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>-16</v>
       </c>
       <c r="I37" s="16" t="n">
-        <v>-307891241</v>
+        <v>-313967878</v>
       </c>
       <c r="J37" s="17" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>55</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>206492027</v>
+        <v>210567418</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>-5</v>
       </c>
       <c r="I38" s="16" t="n">
-        <v>-255360034</v>
+        <v>-260399899</v>
       </c>
       <c r="J38" s="17" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>27</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>181807224</v>
+        <v>185395428</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>21</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>225993630</v>
+        <v>230453911</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>16</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>316403242</v>
+        <v>322647875</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1656,23 +1656,23 @@
       </c>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H48" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>-15449429</v>
+        <v>-205241858</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t>3.94%→4.12%</t>
+          <t>3.84%→3.01%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>313→309</t>
+          <t>21→17</t>
         </is>
       </c>
     </row>
@@ -1700,23 +1700,23 @@
       </c>
       <c r="G49" s="15" t="inlineStr">
         <is>
-          <t>동국산업</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H49" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I49" s="16" t="n">
-        <v>-6919335</v>
+        <v>-213555452</v>
       </c>
       <c r="J49" s="17" t="inlineStr">
         <is>
-          <t>1.83%→1.81%</t>
+          <t>2.91%→2.03%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>307→303</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
@@ -1728,23 +1728,23 @@
       <c r="E50" s="14" t="n"/>
       <c r="G50" s="15" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>동국산업</t>
         </is>
       </c>
       <c r="H50" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>-213555452</v>
+        <v>-6919335</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t>2.91%→2.03%</t>
+          <t>1.83%→1.81%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>307→303</t>
         </is>
       </c>
     </row>
@@ -1756,23 +1756,23 @@
       <c r="E51" s="14" t="n"/>
       <c r="G51" s="15" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="H51" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I51" s="16" t="n">
-        <v>-205241858</v>
+        <v>-15449429</v>
       </c>
       <c r="J51" s="17" t="inlineStr">
         <is>
-          <t>3.84%→3.01%</t>
+          <t>3.94%→4.12%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>21→17</t>
+          <t>313→309</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261019.xlsx
+++ b/reports/pdf_change_20261019.xlsx
@@ -1656,23 +1656,23 @@
       </c>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>동국산업</t>
         </is>
       </c>
       <c r="H48" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>-205241858</v>
+        <v>-6919335</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t>3.84%→3.01%</t>
+          <t>1.83%→1.81%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>21→17</t>
+          <t>307→303</t>
         </is>
       </c>
     </row>
@@ -1700,23 +1700,23 @@
       </c>
       <c r="G49" s="15" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="H49" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I49" s="16" t="n">
-        <v>-213555452</v>
+        <v>-15449429</v>
       </c>
       <c r="J49" s="17" t="inlineStr">
         <is>
-          <t>2.91%→2.03%</t>
+          <t>3.94%→4.12%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>313→309</t>
         </is>
       </c>
     </row>
@@ -1728,23 +1728,23 @@
       <c r="E50" s="14" t="n"/>
       <c r="G50" s="15" t="inlineStr">
         <is>
-          <t>동국산업</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H50" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>-6919335</v>
+        <v>-205241858</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t>1.83%→1.81%</t>
+          <t>3.84%→3.01%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>307→303</t>
+          <t>21→17</t>
         </is>
       </c>
     </row>
@@ -1756,23 +1756,23 @@
       <c r="E51" s="14" t="n"/>
       <c r="G51" s="15" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H51" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I51" s="16" t="n">
-        <v>-15449429</v>
+        <v>-213555452</v>
       </c>
       <c r="J51" s="17" t="inlineStr">
         <is>
-          <t>3.94%→4.12%</t>
+          <t>2.91%→2.03%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>313→309</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261019.xlsx
+++ b/reports/pdf_change_20261019.xlsx
@@ -1656,23 +1656,23 @@
       </c>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>동국산업</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H48" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>-6919335</v>
+        <v>-213555452</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t>1.83%→1.81%</t>
+          <t>2.91%→2.03%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>307→303</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
@@ -1728,23 +1728,23 @@
       <c r="E50" s="14" t="n"/>
       <c r="G50" s="15" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>동국산업</t>
         </is>
       </c>
       <c r="H50" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>-205241858</v>
+        <v>-6919335</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t>3.84%→3.01%</t>
+          <t>1.83%→1.81%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>21→17</t>
+          <t>307→303</t>
         </is>
       </c>
     </row>
@@ -1756,23 +1756,23 @@
       <c r="E51" s="14" t="n"/>
       <c r="G51" s="15" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H51" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I51" s="16" t="n">
-        <v>-213555452</v>
+        <v>-205241858</v>
       </c>
       <c r="J51" s="17" t="inlineStr">
         <is>
-          <t>2.91%→2.03%</t>
+          <t>3.84%→3.01%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>21→17</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261019.xlsx
+++ b/reports/pdf_change_20261019.xlsx
@@ -1656,23 +1656,23 @@
       </c>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>동국산업</t>
         </is>
       </c>
       <c r="H48" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>-213555452</v>
+        <v>-6919335</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t>2.91%→2.03%</t>
+          <t>1.83%→1.81%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>307→303</t>
         </is>
       </c>
     </row>
@@ -1728,23 +1728,23 @@
       <c r="E50" s="14" t="n"/>
       <c r="G50" s="15" t="inlineStr">
         <is>
-          <t>동국산업</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H50" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>-6919335</v>
+        <v>-213555452</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t>1.83%→1.81%</t>
+          <t>2.91%→2.03%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>307→303</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261019.xlsx
+++ b/reports/pdf_change_20261019.xlsx
@@ -1656,23 +1656,23 @@
       </c>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>동국산업</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H48" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>-6919335</v>
+        <v>-213555452</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t>1.83%→1.81%</t>
+          <t>2.91%→2.03%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>307→303</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
@@ -1728,23 +1728,23 @@
       <c r="E50" s="14" t="n"/>
       <c r="G50" s="15" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>동국산업</t>
         </is>
       </c>
       <c r="H50" s="16" t="n">
         <v>-4</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>-213555452</v>
+        <v>-6919335</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t>2.91%→2.03%</t>
+          <t>1.83%→1.81%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>307→303</t>
         </is>
       </c>
     </row>
